--- a/docs/project-management/time-log.xlsx
+++ b/docs/project-management/time-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeffkrystek/Jeff/yek_flashcard/docs/project-management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5A3FE8-0073-F84B-8B39-986B321A332A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF414178-1668-2D4A-92A1-6801EFE5F268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4780" yWindow="3780" windowWidth="27240" windowHeight="16180" xr2:uid="{0105DE84-9EB5-AE49-BB95-638DCEB5FCB9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="49">
   <si>
     <t>Date</t>
   </si>
@@ -89,12 +89,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Planning</t>
-  </si>
-  <si>
-    <t>Charter, Scope, PRD, etc.</t>
-  </si>
-  <si>
     <t>Documentation</t>
   </si>
   <si>
@@ -168,6 +162,30 @@
   </si>
   <si>
     <t>Multiple initiation and planning documents completed</t>
+  </si>
+  <si>
+    <t>finalized Vision Doc and Business Case doc</t>
+  </si>
+  <si>
+    <t>decision to modify docs to include PM docs as co-primary project objective</t>
+  </si>
+  <si>
+    <t>KAN-21, KAN-24</t>
+  </si>
+  <si>
+    <t>finalize Pro-Scope-Stmt, began outline for PRD</t>
+  </si>
+  <si>
+    <t>KAN-10, KAN-13</t>
+  </si>
+  <si>
+    <t>mostly the PRD Func Requirements</t>
+  </si>
+  <si>
+    <t>Jira Stories and tasks from the PRD</t>
+  </si>
+  <si>
+    <t>Sprint Review, Restrospective, Planning</t>
   </si>
 </sst>
 </file>
@@ -549,11 +567,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98788C20-1FDB-4048-9CC4-A8CBA5635041}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="14.33203125" customWidth="1"/>
     <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -658,7 +678,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -675,7 +695,7 @@
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -692,13 +712,13 @@
         <v>14</v>
       </c>
       <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" t="s">
         <v>36</v>
-      </c>
-      <c r="E8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -712,7 +732,7 @@
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -729,13 +749,13 @@
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -749,107 +769,216 @@
         <v>7</v>
       </c>
       <c r="D11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>46229</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>46229</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>46242</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>39</v>
       </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15">
-        <f>SUM(B2:B13)</f>
+      <c r="B20">
+        <f>SUM(B2:B18)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>24</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B28" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" t="s">
         <v>26</v>
       </c>
-      <c r="B24" t="s">
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" t="s">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="B31" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>30</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B32" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/docs/project-management/time-log.xlsx
+++ b/docs/project-management/time-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeffkrystek/Jeff/yek_flashcard/docs/project-management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF414178-1668-2D4A-92A1-6801EFE5F268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{194BCFE9-968D-6A4D-80E0-8A8B01702F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4780" yWindow="3780" windowWidth="27240" windowHeight="16180" xr2:uid="{0105DE84-9EB5-AE49-BB95-638DCEB5FCB9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="53">
   <si>
     <t>Date</t>
   </si>
@@ -186,6 +186,18 @@
   </si>
   <si>
     <t>Sprint Review, Restrospective, Planning</t>
+  </si>
+  <si>
+    <t>Software Architecture Document</t>
+  </si>
+  <si>
+    <t>KAN-60</t>
+  </si>
+  <si>
+    <t>yek Sprint 2</t>
+  </si>
+  <si>
+    <t>general JSON formatting</t>
   </si>
 </sst>
 </file>
@@ -567,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98788C20-1FDB-4048-9CC4-A8CBA5635041}">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -872,7 +884,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>46242</v>
       </c>
@@ -889,95 +901,147 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>46243</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>46243</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="1"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="1"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="1"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>39</v>
       </c>
-      <c r="B20">
-        <f>SUM(B2:B18)</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
+      <c r="B27">
+        <f>SUM(B2:B24)</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B30" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
         <v>16</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B31" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>18</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B32" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
         <v>20</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B33" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
         <v>22</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B34" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
         <v>24</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B35" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
         <v>11</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B36" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
         <v>7</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B37" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
         <v>28</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B38" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
         <v>30</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B39" t="s">
         <v>31</v>
       </c>
     </row>

--- a/docs/project-management/time-log.xlsx
+++ b/docs/project-management/time-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeffkrystek/Jeff/yek_flashcard/docs/project-management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{194BCFE9-968D-6A4D-80E0-8A8B01702F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6EAA2C-F48B-744B-84FA-D84B674A408E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4780" yWindow="3780" windowWidth="27240" windowHeight="16180" xr2:uid="{0105DE84-9EB5-AE49-BB95-638DCEB5FCB9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="56">
   <si>
     <t>Date</t>
   </si>
@@ -198,6 +198,15 @@
   </si>
   <si>
     <t>general JSON formatting</t>
+  </si>
+  <si>
+    <t>decision log needs backfilled</t>
+  </si>
+  <si>
+    <t>KAN-59</t>
+  </si>
+  <si>
+    <t>general category and vocab overview</t>
   </si>
 </sst>
 </file>
@@ -939,10 +948,41 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="1"/>
+      <c r="A20" s="1">
+        <v>46244</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="1"/>
+      <c r="A21" s="1">
+        <v>46244</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
@@ -962,7 +1002,7 @@
       </c>
       <c r="B27">
         <f>SUM(B2:B24)</f>
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">

--- a/docs/project-management/time-log.xlsx
+++ b/docs/project-management/time-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeffkrystek/Jeff/yek_flashcard/docs/project-management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6EAA2C-F48B-744B-84FA-D84B674A408E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878A60C7-8EBD-FA41-9ED4-321AFAD7B147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4780" yWindow="3780" windowWidth="27240" windowHeight="16180" xr2:uid="{0105DE84-9EB5-AE49-BB95-638DCEB5FCB9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="59">
   <si>
     <t>Date</t>
   </si>
@@ -207,6 +207,15 @@
   </si>
   <si>
     <t>general category and vocab overview</t>
+  </si>
+  <si>
+    <t>WBS, Risk Register, Roadmap</t>
+  </si>
+  <si>
+    <t>LLC research</t>
+  </si>
+  <si>
+    <t>KAN-22, KAN-15, KAN-14</t>
   </si>
 </sst>
 </file>
@@ -588,7 +597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98788C20-1FDB-4048-9CC4-A8CBA5635041}">
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -985,10 +994,41 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="1"/>
+      <c r="A22" s="1">
+        <v>46263</v>
+      </c>
+      <c r="B22">
+        <v>4</v>
+      </c>
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" t="s">
+        <v>58</v>
+      </c>
+      <c r="F22" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="1"/>
+      <c r="A23" s="1">
+        <v>46263</v>
+      </c>
+      <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
@@ -996,92 +1036,113 @@
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
     </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="1"/>
+    </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27">
-        <f>SUM(B2:B24)</f>
-        <v>47</v>
-      </c>
+      <c r="A27" s="1"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="1"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="1"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="A30" s="1"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>16</v>
-      </c>
-      <c r="B31" t="s">
-        <v>17</v>
-      </c>
+      <c r="A31" s="1"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>18</v>
-      </c>
-      <c r="B32" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>20</v>
-      </c>
-      <c r="B33" t="s">
-        <v>21</v>
-      </c>
+      <c r="A32" s="1"/>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>22</v>
-      </c>
-      <c r="B34" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>24</v>
-      </c>
-      <c r="B35" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>11</v>
-      </c>
-      <c r="B36" t="s">
-        <v>26</v>
+        <v>39</v>
+      </c>
+      <c r="B34">
+        <f>SUM(B2:B31)</f>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" t="s">
-        <v>27</v>
+      <c r="A37" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B38" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>20</v>
+      </c>
+      <c r="B40" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>24</v>
+      </c>
+      <c r="B42" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>28</v>
+      </c>
+      <c r="B45" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
         <v>30</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B46" t="s">
         <v>31</v>
       </c>
     </row>

--- a/docs/project-management/time-log.xlsx
+++ b/docs/project-management/time-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeffkrystek/Jeff/yek_flashcard/docs/project-management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878A60C7-8EBD-FA41-9ED4-321AFAD7B147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DEC1D2-C750-D946-9C98-CBE39E406EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4780" yWindow="3780" windowWidth="27240" windowHeight="16180" xr2:uid="{0105DE84-9EB5-AE49-BB95-638DCEB5FCB9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="62">
   <si>
     <t>Date</t>
   </si>
@@ -216,6 +216,15 @@
   </si>
   <si>
     <t>KAN-22, KAN-15, KAN-14</t>
+  </si>
+  <si>
+    <t>Accessibility Document</t>
+  </si>
+  <si>
+    <t>KAN-72</t>
+  </si>
+  <si>
+    <t>yek Sprint 3</t>
   </si>
 </sst>
 </file>
@@ -1031,10 +1040,41 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="1"/>
+      <c r="A24" s="1">
+        <v>46270</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="1"/>
+      <c r="A25" s="1">
+        <v>46271</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" t="s">
+        <v>60</v>
+      </c>
+      <c r="F25" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
@@ -1063,7 +1103,7 @@
       </c>
       <c r="B34">
         <f>SUM(B2:B31)</f>
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">

--- a/docs/project-management/time-log.xlsx
+++ b/docs/project-management/time-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeffkrystek/Jeff/yek_flashcard/docs/project-management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DEC1D2-C750-D946-9C98-CBE39E406EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466F4767-DD6E-B94E-86D7-8742165799F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4780" yWindow="3780" windowWidth="27240" windowHeight="16180" xr2:uid="{0105DE84-9EB5-AE49-BB95-638DCEB5FCB9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="63">
   <si>
     <t>Date</t>
   </si>
@@ -225,6 +225,9 @@
   </si>
   <si>
     <t>yek Sprint 3</t>
+  </si>
+  <si>
+    <t>created accounts for various social media</t>
   </si>
 </sst>
 </file>
@@ -1077,7 +1080,21 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="1"/>
+      <c r="A26" s="1">
+        <v>46272</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
@@ -1103,7 +1120,7 @@
       </c>
       <c r="B34">
         <f>SUM(B2:B31)</f>
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">

--- a/docs/project-management/time-log.xlsx
+++ b/docs/project-management/time-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeffkrystek/Jeff/yek_flashcard/docs/project-management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466F4767-DD6E-B94E-86D7-8742165799F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3720856-7B29-6C44-8289-8826931C32E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4780" yWindow="3780" windowWidth="27240" windowHeight="16180" xr2:uid="{0105DE84-9EB5-AE49-BB95-638DCEB5FCB9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="64">
   <si>
     <t>Date</t>
   </si>
@@ -228,6 +228,9 @@
   </si>
   <si>
     <t>created accounts for various social media</t>
+  </si>
+  <si>
+    <t>Porkbun domain sync with GitHub pages</t>
   </si>
 </sst>
 </file>
@@ -1097,7 +1100,21 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="1"/>
+      <c r="A27" s="1">
+        <v>46273</v>
+      </c>
+      <c r="B27">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
@@ -1120,7 +1137,7 @@
       </c>
       <c r="B34">
         <f>SUM(B2:B31)</f>
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">

--- a/docs/project-management/time-log.xlsx
+++ b/docs/project-management/time-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeffkrystek/Jeff/yek_flashcard/docs/project-management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3720856-7B29-6C44-8289-8826931C32E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32BC2980-1AEA-B940-9D6A-81E30A54516C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4780" yWindow="3780" windowWidth="27240" windowHeight="16180" xr2:uid="{0105DE84-9EB5-AE49-BB95-638DCEB5FCB9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="66">
   <si>
     <t>Date</t>
   </si>
@@ -231,6 +231,12 @@
   </si>
   <si>
     <t>Porkbun domain sync with GitHub pages</t>
+  </si>
+  <si>
+    <t>Studying Google Analytics and setting up Brevo</t>
+  </si>
+  <si>
+    <t>Adding cotent and style to website homepage</t>
   </si>
 </sst>
 </file>
@@ -1117,10 +1123,38 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="1"/>
+      <c r="A28" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B28">
+        <v>2</v>
+      </c>
+      <c r="C28" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="1"/>
+      <c r="A29" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+      <c r="C29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" t="s">
+        <v>65</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
@@ -1137,7 +1171,7 @@
       </c>
       <c r="B34">
         <f>SUM(B2:B31)</f>
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">

--- a/docs/project-management/time-log.xlsx
+++ b/docs/project-management/time-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeffkrystek/Jeff/yek_flashcard/docs/project-management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32BC2980-1AEA-B940-9D6A-81E30A54516C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8911429F-BBF7-3C45-B644-D5994B27941D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4780" yWindow="3780" windowWidth="27240" windowHeight="16180" xr2:uid="{0105DE84-9EB5-AE49-BB95-638DCEB5FCB9}"/>
   </bookViews>

--- a/docs/project-management/time-log.xlsx
+++ b/docs/project-management/time-log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeffkrystek/Jeff/yek_flashcard/docs/project-management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8911429F-BBF7-3C45-B644-D5994B27941D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A3CBE8-D8D9-904F-A558-1E2CFC86EFCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4780" yWindow="3780" windowWidth="27240" windowHeight="16180" xr2:uid="{0105DE84-9EB5-AE49-BB95-638DCEB5FCB9}"/>
+    <workbookView xWindow="2740" yWindow="3780" windowWidth="27240" windowHeight="16180" xr2:uid="{0105DE84-9EB5-AE49-BB95-638DCEB5FCB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="66">
   <si>
     <t>Date</t>
   </si>
@@ -1157,7 +1157,21 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="1"/>
+      <c r="A30" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
@@ -1171,7 +1185,7 @@
       </c>
       <c r="B34">
         <f>SUM(B2:B31)</f>
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
